--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40B.xlsx
@@ -121,37 +121,37 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>De satisfacción</t>
+  </si>
+  <si>
+    <t>Socializar el nombre del programa entre los estudiantes para evaluar el impacto de éste entre los beneficiarios directos</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>De satisfacción</t>
-  </si>
-  <si>
-    <t>Socializar el nombre del programa entre los estudiantes para evaluar el impacto de éste entre los beneficiarios directos</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación</t>
-  </si>
-  <si>
-    <t>610140AE8B653655BB4C7CFAE94BD57A</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Sondeo para estudiantes, Fondo de aportación Múltiple 2021</t>
-  </si>
-  <si>
-    <t>http://www.cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202021/Planeacion%20y%20Evaluacion/ENCUESTA%20SATISFACCIÓN%20FAM%2021.pdf</t>
-  </si>
-  <si>
-    <t>15/07/2022</t>
-  </si>
-  <si>
-    <t>En el periodo del 1 de abril de 2022 al 30 de junio de 2022 el Colegio de Bachilleres del Estado de Tlaxcala, no ha  aplicado ninguna encuesta a ningún programa financiado con recursos públicos, por lo que no se cuenta con el hipervínculo correspondiente.</t>
+    <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>Sondeo para estudiantes, Fondo de aportación Múltiple 2022</t>
+  </si>
+  <si>
+    <t>A750BA8F8E7DBAF33AA674A4980CF9D2</t>
+  </si>
+  <si>
+    <t>31/12/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/COBAT/</t>
+  </si>
+  <si>
+    <t>11/01/2023</t>
+  </si>
+  <si>
+    <t>s/n</t>
   </si>
 </sst>
 </file>
@@ -558,7 +558,7 @@
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="221.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="221" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
@@ -721,31 +721,31 @@
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>44</v>
